--- a/Proyecto/docs/Pruebas de Caja Negra_Blanca/Plan_de_Pruebas_Caja_Negra_SistemaPOS_Ge.xlsx
+++ b/Proyecto/docs/Pruebas de Caja Negra_Blanca/Plan_de_Pruebas_Caja_Negra_SistemaPOS_Ge.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="50" documentId="11_2A9B3EB6C3A61F82A6F7471192C7B1FAD6249616" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACC62CAD-0D40-42E4-A69F-C1F69886D906}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tablas de Decisión" sheetId="4" r:id="rId1"/>

--- a/Proyecto/docs/Pruebas de Caja Negra_Blanca/Plan_de_Pruebas_Caja_Negra_SistemaPOS_Ge.xlsx
+++ b/Proyecto/docs/Pruebas de Caja Negra_Blanca/Plan_de_Pruebas_Caja_Negra_SistemaPOS_Ge.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uabcedumx-my.sharepoint.com/personal/joshua_osorio_uabc_edu_mx/Documents/8_Semestre/36289_AnalisisYDisenoDeSistemas/Proyecto/docs/Pruebas de Caja Negra_Blanca/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="11_2A9B3EB6C3A61F82A6F7471192C7B1FAD6249616" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACC62CAD-0D40-42E4-A69F-C1F69886D906}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="11_2A9B3EB6C3A61F82A6F7471192C7B1FAD6249616" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC2B3372-8941-419A-AED1-254F3FF0DF34}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tablas de Decisión" sheetId="4" r:id="rId1"/>
@@ -310,10 +310,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -697,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AD3E710-0B76-4920-9F72-3D7720BE956C}">
-  <dimension ref="B2:F18"/>
+  <dimension ref="B2:F25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="41.7109375" customWidth="1"/>
@@ -900,6 +896,11 @@
       </c>
       <c r="F18" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D25">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
